--- a/2022 data/excel_outputs/36_boothwise_data.xlsx
+++ b/2022 data/excel_outputs/36_boothwise_data.xlsx
@@ -14,11 +14,77 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="436">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="458" uniqueCount="458">
   <si>
     <t>AC 36 Booth-wise Data</t>
   </si>
   <si>
+    <t>Unnamed: 1</t>
+  </si>
+  <si>
+    <t>Unnamed: 2</t>
+  </si>
+  <si>
+    <t>Unnamed: 3</t>
+  </si>
+  <si>
+    <t>Unnamed: 4</t>
+  </si>
+  <si>
+    <t>Unnamed: 5</t>
+  </si>
+  <si>
+    <t>Unnamed: 6</t>
+  </si>
+  <si>
+    <t>Unnamed: 7</t>
+  </si>
+  <si>
+    <t>Unnamed: 8</t>
+  </si>
+  <si>
+    <t>Unnamed: 9</t>
+  </si>
+  <si>
+    <t>Unnamed: 10</t>
+  </si>
+  <si>
+    <t>Unnamed: 11</t>
+  </si>
+  <si>
+    <t>Unnamed: 12</t>
+  </si>
+  <si>
+    <t>Unnamed: 13</t>
+  </si>
+  <si>
+    <t>Unnamed: 14</t>
+  </si>
+  <si>
+    <t>Unnamed: 15</t>
+  </si>
+  <si>
+    <t>Unnamed: 16</t>
+  </si>
+  <si>
+    <t>Unnamed: 17</t>
+  </si>
+  <si>
+    <t>Unnamed: 18</t>
+  </si>
+  <si>
+    <t>Unnamed: 19</t>
+  </si>
+  <si>
+    <t>Unnamed: 20</t>
+  </si>
+  <si>
+    <t>Unnamed: 21</t>
+  </si>
+  <si>
+    <t>Unnamed: 22</t>
+  </si>
+  <si>
     <t>BOOTH ID</t>
   </si>
   <si>
@@ -250,7 +316,7 @@
     <t>75-K.G.V.&amp; SEH. SIMITI BILASPUR, BISHARATNAGAR ROOM NO-02</t>
   </si>
   <si>
-    <t>76-KIRSHI PRASHAR K. BILASPUR SITHIT HUâ€■RMATNAGAR TANDA</t>
+    <t>GURUNANAK GIRLS I. COLLOGE BILASPUR ROOM NO.-03</t>
   </si>
   <si>
     <t>77-MADAR TERESA INTER COLLEGE HURMATNAGAR TANDA ROOM NO 01</t>
@@ -1328,8 +1394,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -1345,7 +1419,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1353,12 +1427,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1657,79 +1749,145 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:23">
-      <c r="A1" t="s">
-        <v>0</v>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:23">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="C2" t="s">
-        <v>415</v>
+        <v>437</v>
       </c>
       <c r="D2" t="s">
-        <v>416</v>
+        <v>438</v>
       </c>
       <c r="E2" t="s">
-        <v>417</v>
+        <v>439</v>
       </c>
       <c r="F2" t="s">
-        <v>418</v>
+        <v>440</v>
       </c>
       <c r="G2" t="s">
-        <v>419</v>
+        <v>441</v>
       </c>
       <c r="H2" t="s">
-        <v>420</v>
+        <v>442</v>
       </c>
       <c r="I2" t="s">
-        <v>421</v>
+        <v>443</v>
       </c>
       <c r="J2" t="s">
-        <v>422</v>
+        <v>444</v>
       </c>
       <c r="K2" t="s">
-        <v>423</v>
+        <v>445</v>
       </c>
       <c r="L2" t="s">
-        <v>424</v>
+        <v>446</v>
       </c>
       <c r="M2" t="s">
-        <v>425</v>
+        <v>447</v>
       </c>
       <c r="N2" t="s">
-        <v>426</v>
+        <v>448</v>
       </c>
       <c r="O2" t="s">
-        <v>427</v>
+        <v>449</v>
       </c>
       <c r="P2" t="s">
-        <v>428</v>
+        <v>450</v>
       </c>
       <c r="Q2" t="s">
-        <v>429</v>
+        <v>451</v>
       </c>
       <c r="R2" t="s">
-        <v>430</v>
+        <v>452</v>
       </c>
       <c r="S2" t="s">
-        <v>431</v>
+        <v>453</v>
       </c>
       <c r="T2" t="s">
-        <v>432</v>
+        <v>454</v>
       </c>
       <c r="U2" t="s">
-        <v>433</v>
+        <v>455</v>
       </c>
       <c r="V2" t="s">
-        <v>434</v>
+        <v>456</v>
       </c>
       <c r="W2" t="s">
-        <v>435</v>
+        <v>457</v>
       </c>
     </row>
     <row r="3" spans="1:23">
@@ -1737,7 +1895,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="C3">
         <v>999</v>
@@ -1808,7 +1966,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="C4">
         <v>828</v>
@@ -1879,7 +2037,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="C5">
         <v>835</v>
@@ -1950,7 +2108,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="C6">
         <v>522</v>
@@ -2021,7 +2179,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="C7">
         <v>512</v>
@@ -2092,7 +2250,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="C8">
         <v>721</v>
@@ -2163,7 +2321,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="C9">
         <v>598</v>
@@ -2234,7 +2392,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="C10">
         <v>788</v>
@@ -2305,7 +2463,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="C11">
         <v>1010</v>
@@ -2376,7 +2534,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="C12">
         <v>1119</v>
@@ -2447,7 +2605,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="C13">
         <v>648</v>
@@ -2518,7 +2676,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="C14">
         <v>734</v>
@@ -2589,7 +2747,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="C15">
         <v>1201</v>
@@ -2660,7 +2818,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C16">
         <v>1164</v>
@@ -2731,7 +2889,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="C17">
         <v>1158</v>
@@ -2802,7 +2960,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="C18">
         <v>873</v>
@@ -2873,7 +3031,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="C19">
         <v>1054</v>
@@ -2944,7 +3102,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="C20">
         <v>929</v>
@@ -3015,7 +3173,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="C21">
         <v>1111</v>
@@ -3086,7 +3244,7 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="C22">
         <v>1099</v>
@@ -3157,7 +3315,7 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="C23">
         <v>806</v>
@@ -3228,7 +3386,7 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="C24">
         <v>1079</v>
@@ -3299,7 +3457,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="C25">
         <v>757</v>
@@ -3370,7 +3528,7 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="C26">
         <v>668</v>
@@ -3441,7 +3599,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="C27">
         <v>819</v>
@@ -3512,7 +3670,7 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="C28">
         <v>725</v>
@@ -3583,7 +3741,7 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>29</v>
+        <v>51</v>
       </c>
       <c r="C29">
         <v>743</v>
@@ -3654,7 +3812,7 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>30</v>
+        <v>52</v>
       </c>
       <c r="C30">
         <v>678</v>
@@ -3725,7 +3883,7 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="C31">
         <v>853</v>
@@ -3796,7 +3954,7 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="C32">
         <v>1153</v>
@@ -3867,7 +4025,7 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="C33">
         <v>1118</v>
@@ -3938,7 +4096,7 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="C34">
         <v>892</v>
@@ -4009,7 +4167,7 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>35</v>
+        <v>57</v>
       </c>
       <c r="C35">
         <v>641</v>
@@ -4080,7 +4238,7 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="C36">
         <v>629</v>
@@ -4151,7 +4309,7 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>37</v>
+        <v>59</v>
       </c>
       <c r="C37">
         <v>807</v>
@@ -4222,7 +4380,7 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="C38">
         <v>690</v>
@@ -4293,7 +4451,7 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>39</v>
+        <v>61</v>
       </c>
       <c r="C39">
         <v>791</v>
@@ -4364,7 +4522,7 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="C40">
         <v>493</v>
@@ -4435,7 +4593,7 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>41</v>
+        <v>63</v>
       </c>
       <c r="C41">
         <v>1083</v>
@@ -4506,7 +4664,7 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="C42">
         <v>779</v>
@@ -4577,7 +4735,7 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="C43">
         <v>358</v>
@@ -4648,7 +4806,7 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="C44">
         <v>728</v>
@@ -4719,7 +4877,7 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>45</v>
+        <v>67</v>
       </c>
       <c r="C45">
         <v>556</v>
@@ -4790,7 +4948,7 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="C46">
         <v>655</v>
@@ -4861,7 +5019,7 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>47</v>
+        <v>69</v>
       </c>
       <c r="C47">
         <v>650</v>
@@ -4932,7 +5090,7 @@
         <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="C48">
         <v>778</v>
@@ -5003,7 +5161,7 @@
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>49</v>
+        <v>71</v>
       </c>
       <c r="C49">
         <v>760</v>
@@ -5074,7 +5232,7 @@
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="C50">
         <v>949</v>
@@ -5145,7 +5303,7 @@
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>51</v>
+        <v>73</v>
       </c>
       <c r="C51">
         <v>716</v>
@@ -5216,7 +5374,7 @@
         <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>52</v>
+        <v>74</v>
       </c>
       <c r="C52">
         <v>481</v>
@@ -5287,7 +5445,7 @@
         <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="C53">
         <v>705</v>
@@ -5358,7 +5516,7 @@
         <v>52</v>
       </c>
       <c r="B54" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="C54">
         <v>664</v>
@@ -5429,7 +5587,7 @@
         <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>55</v>
+        <v>77</v>
       </c>
       <c r="C55">
         <v>553</v>
@@ -5500,7 +5658,7 @@
         <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>56</v>
+        <v>78</v>
       </c>
       <c r="C56">
         <v>986</v>
@@ -5571,7 +5729,7 @@
         <v>55</v>
       </c>
       <c r="B57" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="C57">
         <v>1047</v>
@@ -5642,7 +5800,7 @@
         <v>56</v>
       </c>
       <c r="B58" t="s">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="C58">
         <v>1076</v>
@@ -5713,7 +5871,7 @@
         <v>57</v>
       </c>
       <c r="B59" t="s">
-        <v>59</v>
+        <v>81</v>
       </c>
       <c r="C59">
         <v>353</v>
@@ -5784,7 +5942,7 @@
         <v>58</v>
       </c>
       <c r="B60" t="s">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="C60">
         <v>698</v>
@@ -5855,7 +6013,7 @@
         <v>59</v>
       </c>
       <c r="B61" t="s">
-        <v>61</v>
+        <v>83</v>
       </c>
       <c r="C61">
         <v>699</v>
@@ -5926,7 +6084,7 @@
         <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>62</v>
+        <v>84</v>
       </c>
       <c r="C62">
         <v>1049</v>
@@ -5997,7 +6155,7 @@
         <v>61</v>
       </c>
       <c r="B63" t="s">
-        <v>63</v>
+        <v>85</v>
       </c>
       <c r="C63">
         <v>1099</v>
@@ -6068,7 +6226,7 @@
         <v>62</v>
       </c>
       <c r="B64" t="s">
-        <v>64</v>
+        <v>86</v>
       </c>
       <c r="C64">
         <v>899</v>
@@ -6139,7 +6297,7 @@
         <v>63</v>
       </c>
       <c r="B65" t="s">
-        <v>65</v>
+        <v>87</v>
       </c>
       <c r="C65">
         <v>904</v>
@@ -6210,7 +6368,7 @@
         <v>64</v>
       </c>
       <c r="B66" t="s">
-        <v>66</v>
+        <v>88</v>
       </c>
       <c r="C66">
         <v>903</v>
@@ -6281,7 +6439,7 @@
         <v>65</v>
       </c>
       <c r="B67" t="s">
-        <v>67</v>
+        <v>89</v>
       </c>
       <c r="C67">
         <v>790</v>
@@ -6352,7 +6510,7 @@
         <v>66</v>
       </c>
       <c r="B68" t="s">
-        <v>68</v>
+        <v>90</v>
       </c>
       <c r="C68">
         <v>1180</v>
@@ -6423,7 +6581,7 @@
         <v>67</v>
       </c>
       <c r="B69" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="C69">
         <v>1039</v>
@@ -6494,7 +6652,7 @@
         <v>68</v>
       </c>
       <c r="B70" t="s">
-        <v>70</v>
+        <v>92</v>
       </c>
       <c r="C70">
         <v>593</v>
@@ -6565,7 +6723,7 @@
         <v>69</v>
       </c>
       <c r="B71" t="s">
-        <v>71</v>
+        <v>93</v>
       </c>
       <c r="C71">
         <v>781</v>
@@ -6636,7 +6794,7 @@
         <v>70</v>
       </c>
       <c r="B72" t="s">
-        <v>72</v>
+        <v>94</v>
       </c>
       <c r="C72">
         <v>1052</v>
@@ -6707,7 +6865,7 @@
         <v>71</v>
       </c>
       <c r="B73" t="s">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="C73">
         <v>1198</v>
@@ -6778,7 +6936,7 @@
         <v>72</v>
       </c>
       <c r="B74" t="s">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="C74">
         <v>550</v>
@@ -6849,7 +7007,7 @@
         <v>73</v>
       </c>
       <c r="B75" t="s">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="C75">
         <v>535</v>
@@ -6920,7 +7078,7 @@
         <v>74</v>
       </c>
       <c r="B76" t="s">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="C76">
         <v>1085</v>
@@ -6991,7 +7149,7 @@
         <v>75</v>
       </c>
       <c r="B77" t="s">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="C77">
         <v>1032</v>
@@ -7062,7 +7220,7 @@
         <v>76</v>
       </c>
       <c r="B78" t="s">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="C78">
         <v>978</v>
@@ -7133,7 +7291,7 @@
         <v>77</v>
       </c>
       <c r="B79" t="s">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="C79">
         <v>716</v>
@@ -7204,7 +7362,7 @@
         <v>78</v>
       </c>
       <c r="B80" t="s">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="C80">
         <v>667</v>
@@ -7275,7 +7433,7 @@
         <v>79</v>
       </c>
       <c r="B81" t="s">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="C81">
         <v>1151</v>
@@ -7346,7 +7504,7 @@
         <v>80</v>
       </c>
       <c r="B82" t="s">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="C82">
         <v>1188</v>
@@ -7417,7 +7575,7 @@
         <v>81</v>
       </c>
       <c r="B83" t="s">
-        <v>83</v>
+        <v>105</v>
       </c>
       <c r="C83">
         <v>1106</v>
@@ -7488,7 +7646,7 @@
         <v>82</v>
       </c>
       <c r="B84" t="s">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="C84">
         <v>1047</v>
@@ -7559,7 +7717,7 @@
         <v>83</v>
       </c>
       <c r="B85" t="s">
-        <v>85</v>
+        <v>107</v>
       </c>
       <c r="C85">
         <v>1039</v>
@@ -7630,7 +7788,7 @@
         <v>84</v>
       </c>
       <c r="B86" t="s">
-        <v>86</v>
+        <v>108</v>
       </c>
       <c r="C86">
         <v>724</v>
@@ -7701,7 +7859,7 @@
         <v>85</v>
       </c>
       <c r="B87" t="s">
-        <v>87</v>
+        <v>109</v>
       </c>
       <c r="C87">
         <v>879</v>
@@ -7772,7 +7930,7 @@
         <v>86</v>
       </c>
       <c r="B88" t="s">
-        <v>88</v>
+        <v>110</v>
       </c>
       <c r="C88">
         <v>1153</v>
@@ -7843,7 +8001,7 @@
         <v>87</v>
       </c>
       <c r="B89" t="s">
-        <v>89</v>
+        <v>111</v>
       </c>
       <c r="C89">
         <v>994</v>
@@ -7914,7 +8072,7 @@
         <v>88</v>
       </c>
       <c r="B90" t="s">
-        <v>90</v>
+        <v>112</v>
       </c>
       <c r="C90">
         <v>665</v>
@@ -7985,7 +8143,7 @@
         <v>89</v>
       </c>
       <c r="B91" t="s">
-        <v>91</v>
+        <v>113</v>
       </c>
       <c r="C91">
         <v>617</v>
@@ -8056,7 +8214,7 @@
         <v>90</v>
       </c>
       <c r="B92" t="s">
-        <v>92</v>
+        <v>114</v>
       </c>
       <c r="C92">
         <v>984</v>
@@ -8127,7 +8285,7 @@
         <v>91</v>
       </c>
       <c r="B93" t="s">
-        <v>93</v>
+        <v>115</v>
       </c>
       <c r="C93">
         <v>1021</v>
@@ -8198,7 +8356,7 @@
         <v>92</v>
       </c>
       <c r="B94" t="s">
-        <v>94</v>
+        <v>116</v>
       </c>
       <c r="C94">
         <v>1132</v>
@@ -8269,7 +8427,7 @@
         <v>93</v>
       </c>
       <c r="B95" t="s">
-        <v>95</v>
+        <v>117</v>
       </c>
       <c r="C95">
         <v>1042</v>
@@ -8340,7 +8498,7 @@
         <v>94</v>
       </c>
       <c r="B96" t="s">
-        <v>96</v>
+        <v>118</v>
       </c>
       <c r="C96">
         <v>1007</v>
@@ -8411,7 +8569,7 @@
         <v>95</v>
       </c>
       <c r="B97" t="s">
-        <v>97</v>
+        <v>119</v>
       </c>
       <c r="C97">
         <v>822</v>
@@ -8482,7 +8640,7 @@
         <v>96</v>
       </c>
       <c r="B98" t="s">
-        <v>98</v>
+        <v>120</v>
       </c>
       <c r="C98">
         <v>905</v>
@@ -8553,7 +8711,7 @@
         <v>97</v>
       </c>
       <c r="B99" t="s">
-        <v>99</v>
+        <v>121</v>
       </c>
       <c r="C99">
         <v>758</v>
@@ -8624,7 +8782,7 @@
         <v>98</v>
       </c>
       <c r="B100" t="s">
-        <v>100</v>
+        <v>122</v>
       </c>
       <c r="C100">
         <v>876</v>
@@ -8695,7 +8853,7 @@
         <v>99</v>
       </c>
       <c r="B101" t="s">
-        <v>101</v>
+        <v>123</v>
       </c>
       <c r="C101">
         <v>1175</v>
@@ -8766,7 +8924,7 @@
         <v>100</v>
       </c>
       <c r="B102" t="s">
-        <v>102</v>
+        <v>124</v>
       </c>
       <c r="C102">
         <v>951</v>
@@ -8837,7 +8995,7 @@
         <v>101</v>
       </c>
       <c r="B103" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="C103">
         <v>757</v>
@@ -8908,7 +9066,7 @@
         <v>102</v>
       </c>
       <c r="B104" t="s">
-        <v>104</v>
+        <v>126</v>
       </c>
       <c r="C104">
         <v>885</v>
@@ -8979,7 +9137,7 @@
         <v>103</v>
       </c>
       <c r="B105" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="C105">
         <v>971</v>
@@ -9050,7 +9208,7 @@
         <v>104</v>
       </c>
       <c r="B106" t="s">
-        <v>106</v>
+        <v>128</v>
       </c>
       <c r="C106">
         <v>906</v>
@@ -9121,7 +9279,7 @@
         <v>105</v>
       </c>
       <c r="B107" t="s">
-        <v>107</v>
+        <v>129</v>
       </c>
       <c r="C107">
         <v>1050</v>
@@ -9192,7 +9350,7 @@
         <v>106</v>
       </c>
       <c r="B108" t="s">
-        <v>108</v>
+        <v>130</v>
       </c>
       <c r="C108">
         <v>1103</v>
@@ -9263,7 +9421,7 @@
         <v>107</v>
       </c>
       <c r="B109" t="s">
-        <v>109</v>
+        <v>131</v>
       </c>
       <c r="C109">
         <v>1043</v>
@@ -9334,7 +9492,7 @@
         <v>108</v>
       </c>
       <c r="B110" t="s">
-        <v>110</v>
+        <v>132</v>
       </c>
       <c r="C110">
         <v>691</v>
@@ -9405,7 +9563,7 @@
         <v>109</v>
       </c>
       <c r="B111" t="s">
-        <v>111</v>
+        <v>133</v>
       </c>
       <c r="C111">
         <v>641</v>
@@ -9476,7 +9634,7 @@
         <v>110</v>
       </c>
       <c r="B112" t="s">
-        <v>112</v>
+        <v>134</v>
       </c>
       <c r="C112">
         <v>723</v>
@@ -9547,7 +9705,7 @@
         <v>111</v>
       </c>
       <c r="B113" t="s">
-        <v>113</v>
+        <v>135</v>
       </c>
       <c r="C113">
         <v>668</v>
@@ -9618,7 +9776,7 @@
         <v>112</v>
       </c>
       <c r="B114" t="s">
-        <v>114</v>
+        <v>136</v>
       </c>
       <c r="C114">
         <v>888</v>
@@ -9689,7 +9847,7 @@
         <v>113</v>
       </c>
       <c r="B115" t="s">
-        <v>115</v>
+        <v>137</v>
       </c>
       <c r="C115">
         <v>809</v>
@@ -9760,7 +9918,7 @@
         <v>114</v>
       </c>
       <c r="B116" t="s">
-        <v>116</v>
+        <v>138</v>
       </c>
       <c r="C116">
         <v>938</v>
@@ -9831,7 +9989,7 @@
         <v>115</v>
       </c>
       <c r="B117" t="s">
-        <v>117</v>
+        <v>139</v>
       </c>
       <c r="C117">
         <v>924</v>
@@ -9902,7 +10060,7 @@
         <v>116</v>
       </c>
       <c r="B118" t="s">
-        <v>118</v>
+        <v>140</v>
       </c>
       <c r="C118">
         <v>938</v>
@@ -9973,7 +10131,7 @@
         <v>117</v>
       </c>
       <c r="B119" t="s">
-        <v>119</v>
+        <v>141</v>
       </c>
       <c r="C119">
         <v>1199</v>
@@ -10044,7 +10202,7 @@
         <v>118</v>
       </c>
       <c r="B120" t="s">
-        <v>120</v>
+        <v>142</v>
       </c>
       <c r="C120">
         <v>671</v>
@@ -10115,7 +10273,7 @@
         <v>119</v>
       </c>
       <c r="B121" t="s">
-        <v>121</v>
+        <v>143</v>
       </c>
       <c r="C121">
         <v>760</v>
@@ -10186,7 +10344,7 @@
         <v>120</v>
       </c>
       <c r="B122" t="s">
-        <v>122</v>
+        <v>144</v>
       </c>
       <c r="C122">
         <v>1150</v>
@@ -10257,7 +10415,7 @@
         <v>121</v>
       </c>
       <c r="B123" t="s">
-        <v>123</v>
+        <v>145</v>
       </c>
       <c r="C123">
         <v>925</v>
@@ -10328,7 +10486,7 @@
         <v>122</v>
       </c>
       <c r="B124" t="s">
-        <v>124</v>
+        <v>146</v>
       </c>
       <c r="C124">
         <v>1100</v>
@@ -10399,7 +10557,7 @@
         <v>123</v>
       </c>
       <c r="B125" t="s">
-        <v>125</v>
+        <v>147</v>
       </c>
       <c r="C125">
         <v>1185</v>
@@ -10470,7 +10628,7 @@
         <v>124</v>
       </c>
       <c r="B126" t="s">
-        <v>126</v>
+        <v>148</v>
       </c>
       <c r="C126">
         <v>1184</v>
@@ -10541,7 +10699,7 @@
         <v>125</v>
       </c>
       <c r="B127" t="s">
-        <v>127</v>
+        <v>149</v>
       </c>
       <c r="C127">
         <v>887</v>
@@ -10612,7 +10770,7 @@
         <v>126</v>
       </c>
       <c r="B128" t="s">
-        <v>128</v>
+        <v>150</v>
       </c>
       <c r="C128">
         <v>526</v>
@@ -10683,7 +10841,7 @@
         <v>127</v>
       </c>
       <c r="B129" t="s">
-        <v>129</v>
+        <v>151</v>
       </c>
       <c r="C129">
         <v>1135</v>
@@ -10754,7 +10912,7 @@
         <v>128</v>
       </c>
       <c r="B130" t="s">
-        <v>130</v>
+        <v>152</v>
       </c>
       <c r="C130">
         <v>907</v>
@@ -10825,7 +10983,7 @@
         <v>129</v>
       </c>
       <c r="B131" t="s">
-        <v>131</v>
+        <v>153</v>
       </c>
       <c r="C131">
         <v>673</v>
@@ -10896,7 +11054,7 @@
         <v>130</v>
       </c>
       <c r="B132" t="s">
-        <v>132</v>
+        <v>154</v>
       </c>
       <c r="C132">
         <v>715</v>
@@ -10967,7 +11125,7 @@
         <v>131</v>
       </c>
       <c r="B133" t="s">
-        <v>133</v>
+        <v>155</v>
       </c>
       <c r="C133">
         <v>718</v>
@@ -11038,7 +11196,7 @@
         <v>132</v>
       </c>
       <c r="B134" t="s">
-        <v>134</v>
+        <v>156</v>
       </c>
       <c r="C134">
         <v>628</v>
@@ -11109,7 +11267,7 @@
         <v>133</v>
       </c>
       <c r="B135" t="s">
-        <v>135</v>
+        <v>157</v>
       </c>
       <c r="C135">
         <v>610</v>
@@ -11180,7 +11338,7 @@
         <v>134</v>
       </c>
       <c r="B136" t="s">
-        <v>136</v>
+        <v>158</v>
       </c>
       <c r="C136">
         <v>881</v>
@@ -11251,7 +11409,7 @@
         <v>135</v>
       </c>
       <c r="B137" t="s">
-        <v>137</v>
+        <v>159</v>
       </c>
       <c r="C137">
         <v>752</v>
@@ -11322,7 +11480,7 @@
         <v>136</v>
       </c>
       <c r="B138" t="s">
-        <v>138</v>
+        <v>160</v>
       </c>
       <c r="C138">
         <v>699</v>
@@ -11393,7 +11551,7 @@
         <v>137</v>
       </c>
       <c r="B139" t="s">
-        <v>139</v>
+        <v>161</v>
       </c>
       <c r="C139">
         <v>779</v>
@@ -11464,7 +11622,7 @@
         <v>138</v>
       </c>
       <c r="B140" t="s">
-        <v>140</v>
+        <v>162</v>
       </c>
       <c r="C140">
         <v>1082</v>
@@ -11535,7 +11693,7 @@
         <v>139</v>
       </c>
       <c r="B141" t="s">
-        <v>141</v>
+        <v>163</v>
       </c>
       <c r="C141">
         <v>987</v>
@@ -11606,7 +11764,7 @@
         <v>140</v>
       </c>
       <c r="B142" t="s">
-        <v>142</v>
+        <v>164</v>
       </c>
       <c r="C142">
         <v>1054</v>
@@ -11677,7 +11835,7 @@
         <v>141</v>
       </c>
       <c r="B143" t="s">
-        <v>143</v>
+        <v>165</v>
       </c>
       <c r="C143">
         <v>980</v>
@@ -11748,7 +11906,7 @@
         <v>142</v>
       </c>
       <c r="B144" t="s">
-        <v>144</v>
+        <v>166</v>
       </c>
       <c r="C144">
         <v>1021</v>
@@ -11819,7 +11977,7 @@
         <v>143</v>
       </c>
       <c r="B145" t="s">
-        <v>145</v>
+        <v>167</v>
       </c>
       <c r="C145">
         <v>547</v>
@@ -11890,7 +12048,7 @@
         <v>144</v>
       </c>
       <c r="B146" t="s">
-        <v>146</v>
+        <v>168</v>
       </c>
       <c r="C146">
         <v>492</v>
@@ -11961,7 +12119,7 @@
         <v>145</v>
       </c>
       <c r="B147" t="s">
-        <v>147</v>
+        <v>169</v>
       </c>
       <c r="C147">
         <v>860</v>
@@ -12032,7 +12190,7 @@
         <v>146</v>
       </c>
       <c r="B148" t="s">
-        <v>148</v>
+        <v>170</v>
       </c>
       <c r="C148">
         <v>980</v>
@@ -12103,7 +12261,7 @@
         <v>147</v>
       </c>
       <c r="B149" t="s">
-        <v>149</v>
+        <v>171</v>
       </c>
       <c r="C149">
         <v>892</v>
@@ -12174,7 +12332,7 @@
         <v>148</v>
       </c>
       <c r="B150" t="s">
-        <v>150</v>
+        <v>172</v>
       </c>
       <c r="C150">
         <v>660</v>
@@ -12245,7 +12403,7 @@
         <v>149</v>
       </c>
       <c r="B151" t="s">
-        <v>151</v>
+        <v>173</v>
       </c>
       <c r="C151">
         <v>560</v>
@@ -12316,7 +12474,7 @@
         <v>150</v>
       </c>
       <c r="B152" t="s">
-        <v>152</v>
+        <v>174</v>
       </c>
       <c r="C152">
         <v>1032</v>
@@ -12387,7 +12545,7 @@
         <v>151</v>
       </c>
       <c r="B153" t="s">
-        <v>153</v>
+        <v>175</v>
       </c>
       <c r="C153">
         <v>1104</v>
@@ -12458,7 +12616,7 @@
         <v>152</v>
       </c>
       <c r="B154" t="s">
-        <v>154</v>
+        <v>176</v>
       </c>
       <c r="C154">
         <v>860</v>
@@ -12529,7 +12687,7 @@
         <v>153</v>
       </c>
       <c r="B155" t="s">
-        <v>155</v>
+        <v>177</v>
       </c>
       <c r="C155">
         <v>867</v>
@@ -12600,7 +12758,7 @@
         <v>154</v>
       </c>
       <c r="B156" t="s">
-        <v>156</v>
+        <v>178</v>
       </c>
       <c r="C156">
         <v>618</v>
@@ -12671,7 +12829,7 @@
         <v>155</v>
       </c>
       <c r="B157" t="s">
-        <v>157</v>
+        <v>179</v>
       </c>
       <c r="C157">
         <v>724</v>
@@ -12742,7 +12900,7 @@
         <v>156</v>
       </c>
       <c r="B158" t="s">
-        <v>158</v>
+        <v>180</v>
       </c>
       <c r="C158">
         <v>1135</v>
@@ -12813,7 +12971,7 @@
         <v>157</v>
       </c>
       <c r="B159" t="s">
-        <v>159</v>
+        <v>181</v>
       </c>
       <c r="C159">
         <v>696</v>
@@ -12884,7 +13042,7 @@
         <v>158</v>
       </c>
       <c r="B160" t="s">
-        <v>160</v>
+        <v>182</v>
       </c>
       <c r="C160">
         <v>740</v>
@@ -12955,7 +13113,7 @@
         <v>159</v>
       </c>
       <c r="B161" t="s">
-        <v>161</v>
+        <v>183</v>
       </c>
       <c r="C161">
         <v>1094</v>
@@ -13026,7 +13184,7 @@
         <v>160</v>
       </c>
       <c r="B162" t="s">
-        <v>162</v>
+        <v>184</v>
       </c>
       <c r="C162">
         <v>644</v>
@@ -13097,7 +13255,7 @@
         <v>161</v>
       </c>
       <c r="B163" t="s">
-        <v>163</v>
+        <v>185</v>
       </c>
       <c r="C163">
         <v>921</v>
@@ -13168,7 +13326,7 @@
         <v>162</v>
       </c>
       <c r="B164" t="s">
-        <v>164</v>
+        <v>186</v>
       </c>
       <c r="C164">
         <v>627</v>
@@ -13239,7 +13397,7 @@
         <v>163</v>
       </c>
       <c r="B165" t="s">
-        <v>165</v>
+        <v>187</v>
       </c>
       <c r="C165">
         <v>899</v>
@@ -13310,7 +13468,7 @@
         <v>164</v>
       </c>
       <c r="B166" t="s">
-        <v>166</v>
+        <v>188</v>
       </c>
       <c r="C166">
         <v>674</v>
@@ -13381,7 +13539,7 @@
         <v>165</v>
       </c>
       <c r="B167" t="s">
-        <v>167</v>
+        <v>189</v>
       </c>
       <c r="C167">
         <v>935</v>
@@ -13452,7 +13610,7 @@
         <v>166</v>
       </c>
       <c r="B168" t="s">
-        <v>168</v>
+        <v>190</v>
       </c>
       <c r="C168">
         <v>1059</v>
@@ -13523,7 +13681,7 @@
         <v>167</v>
       </c>
       <c r="B169" t="s">
-        <v>169</v>
+        <v>191</v>
       </c>
       <c r="C169">
         <v>531</v>
@@ -13594,7 +13752,7 @@
         <v>168</v>
       </c>
       <c r="B170" t="s">
-        <v>170</v>
+        <v>192</v>
       </c>
       <c r="C170">
         <v>584</v>
@@ -13665,7 +13823,7 @@
         <v>169</v>
       </c>
       <c r="B171" t="s">
-        <v>171</v>
+        <v>193</v>
       </c>
       <c r="C171">
         <v>1159</v>
@@ -13736,7 +13894,7 @@
         <v>170</v>
       </c>
       <c r="B172" t="s">
-        <v>172</v>
+        <v>194</v>
       </c>
       <c r="C172">
         <v>1096</v>
@@ -13807,7 +13965,7 @@
         <v>171</v>
       </c>
       <c r="B173" t="s">
-        <v>173</v>
+        <v>195</v>
       </c>
       <c r="C173">
         <v>484</v>
@@ -13878,7 +14036,7 @@
         <v>172</v>
       </c>
       <c r="B174" t="s">
-        <v>174</v>
+        <v>196</v>
       </c>
       <c r="C174">
         <v>1019</v>
@@ -13949,7 +14107,7 @@
         <v>173</v>
       </c>
       <c r="B175" t="s">
-        <v>175</v>
+        <v>197</v>
       </c>
       <c r="C175">
         <v>905</v>
@@ -14020,7 +14178,7 @@
         <v>174</v>
       </c>
       <c r="B176" t="s">
-        <v>176</v>
+        <v>198</v>
       </c>
       <c r="C176">
         <v>1145</v>
@@ -14091,7 +14249,7 @@
         <v>175</v>
       </c>
       <c r="B177" t="s">
-        <v>177</v>
+        <v>199</v>
       </c>
       <c r="C177">
         <v>1129</v>
@@ -14162,7 +14320,7 @@
         <v>176</v>
       </c>
       <c r="B178" t="s">
-        <v>178</v>
+        <v>200</v>
       </c>
       <c r="C178">
         <v>1090</v>
@@ -14233,7 +14391,7 @@
         <v>177</v>
       </c>
       <c r="B179" t="s">
-        <v>179</v>
+        <v>201</v>
       </c>
       <c r="C179">
         <v>988</v>
@@ -14304,7 +14462,7 @@
         <v>178</v>
       </c>
       <c r="B180" t="s">
-        <v>180</v>
+        <v>202</v>
       </c>
       <c r="C180">
         <v>863</v>
@@ -14375,7 +14533,7 @@
         <v>179</v>
       </c>
       <c r="B181" t="s">
-        <v>181</v>
+        <v>203</v>
       </c>
       <c r="C181">
         <v>1116</v>
@@ -14446,7 +14604,7 @@
         <v>180</v>
       </c>
       <c r="B182" t="s">
-        <v>182</v>
+        <v>204</v>
       </c>
       <c r="C182">
         <v>408</v>
@@ -14517,7 +14675,7 @@
         <v>181</v>
       </c>
       <c r="B183" t="s">
-        <v>183</v>
+        <v>205</v>
       </c>
       <c r="C183">
         <v>588</v>
@@ -14588,7 +14746,7 @@
         <v>182</v>
       </c>
       <c r="B184" t="s">
-        <v>184</v>
+        <v>206</v>
       </c>
       <c r="C184">
         <v>1119</v>
@@ -14659,7 +14817,7 @@
         <v>183</v>
       </c>
       <c r="B185" t="s">
-        <v>185</v>
+        <v>207</v>
       </c>
       <c r="C185">
         <v>800</v>
@@ -14730,7 +14888,7 @@
         <v>184</v>
       </c>
       <c r="B186" t="s">
-        <v>186</v>
+        <v>208</v>
       </c>
       <c r="C186">
         <v>874</v>
@@ -14801,7 +14959,7 @@
         <v>185</v>
       </c>
       <c r="B187" t="s">
-        <v>187</v>
+        <v>209</v>
       </c>
       <c r="C187">
         <v>814</v>
@@ -14872,7 +15030,7 @@
         <v>186</v>
       </c>
       <c r="B188" t="s">
-        <v>188</v>
+        <v>210</v>
       </c>
       <c r="C188">
         <v>845</v>
@@ -14943,7 +15101,7 @@
         <v>187</v>
       </c>
       <c r="B189" t="s">
-        <v>189</v>
+        <v>211</v>
       </c>
       <c r="C189">
         <v>632</v>
@@ -15014,7 +15172,7 @@
         <v>188</v>
       </c>
       <c r="B190" t="s">
-        <v>190</v>
+        <v>212</v>
       </c>
       <c r="C190">
         <v>626</v>
@@ -15085,7 +15243,7 @@
         <v>189</v>
       </c>
       <c r="B191" t="s">
-        <v>191</v>
+        <v>213</v>
       </c>
       <c r="C191">
         <v>1032</v>
@@ -15156,7 +15314,7 @@
         <v>190</v>
       </c>
       <c r="B192" t="s">
-        <v>192</v>
+        <v>214</v>
       </c>
       <c r="C192">
         <v>1180</v>
@@ -15227,7 +15385,7 @@
         <v>191</v>
       </c>
       <c r="B193" t="s">
-        <v>193</v>
+        <v>215</v>
       </c>
       <c r="C193">
         <v>1090</v>
@@ -15298,7 +15456,7 @@
         <v>192</v>
       </c>
       <c r="B194" t="s">
-        <v>194</v>
+        <v>216</v>
       </c>
       <c r="C194">
         <v>1075</v>
@@ -15369,7 +15527,7 @@
         <v>193</v>
       </c>
       <c r="B195" t="s">
-        <v>195</v>
+        <v>217</v>
       </c>
       <c r="C195">
         <v>967</v>
@@ -15440,7 +15598,7 @@
         <v>194</v>
       </c>
       <c r="B196" t="s">
-        <v>196</v>
+        <v>218</v>
       </c>
       <c r="C196">
         <v>1163</v>
@@ -15511,7 +15669,7 @@
         <v>195</v>
       </c>
       <c r="B197" t="s">
-        <v>197</v>
+        <v>219</v>
       </c>
       <c r="C197">
         <v>891</v>
@@ -15582,7 +15740,7 @@
         <v>196</v>
       </c>
       <c r="B198" t="s">
-        <v>198</v>
+        <v>220</v>
       </c>
       <c r="C198">
         <v>590</v>
@@ -15653,7 +15811,7 @@
         <v>197</v>
       </c>
       <c r="B199" t="s">
-        <v>199</v>
+        <v>221</v>
       </c>
       <c r="C199">
         <v>1067</v>
@@ -15724,7 +15882,7 @@
         <v>198</v>
       </c>
       <c r="B200" t="s">
-        <v>200</v>
+        <v>222</v>
       </c>
       <c r="C200">
         <v>864</v>
@@ -15795,7 +15953,7 @@
         <v>199</v>
       </c>
       <c r="B201" t="s">
-        <v>201</v>
+        <v>223</v>
       </c>
       <c r="C201">
         <v>941</v>
@@ -15866,7 +16024,7 @@
         <v>200</v>
       </c>
       <c r="B202" t="s">
-        <v>202</v>
+        <v>224</v>
       </c>
       <c r="C202">
         <v>994</v>
@@ -15937,7 +16095,7 @@
         <v>201</v>
       </c>
       <c r="B203" t="s">
-        <v>203</v>
+        <v>225</v>
       </c>
       <c r="C203">
         <v>555</v>
@@ -16008,7 +16166,7 @@
         <v>202</v>
       </c>
       <c r="B204" t="s">
-        <v>204</v>
+        <v>226</v>
       </c>
       <c r="C204">
         <v>977</v>
@@ -16079,7 +16237,7 @@
         <v>203</v>
       </c>
       <c r="B205" t="s">
-        <v>205</v>
+        <v>227</v>
       </c>
       <c r="C205">
         <v>737</v>
@@ -16150,7 +16308,7 @@
         <v>204</v>
       </c>
       <c r="B206" t="s">
-        <v>206</v>
+        <v>228</v>
       </c>
       <c r="C206">
         <v>659</v>
@@ -16221,7 +16379,7 @@
         <v>205</v>
       </c>
       <c r="B207" t="s">
-        <v>207</v>
+        <v>229</v>
       </c>
       <c r="C207">
         <v>1020</v>
@@ -16292,7 +16450,7 @@
         <v>206</v>
       </c>
       <c r="B208" t="s">
-        <v>208</v>
+        <v>230</v>
       </c>
       <c r="C208">
         <v>882</v>
@@ -16363,7 +16521,7 @@
         <v>207</v>
       </c>
       <c r="B209" t="s">
-        <v>209</v>
+        <v>231</v>
       </c>
       <c r="C209">
         <v>755</v>
@@ -16434,7 +16592,7 @@
         <v>208</v>
       </c>
       <c r="B210" t="s">
-        <v>210</v>
+        <v>232</v>
       </c>
       <c r="C210">
         <v>579</v>
@@ -16505,7 +16663,7 @@
         <v>209</v>
       </c>
       <c r="B211" t="s">
-        <v>211</v>
+        <v>233</v>
       </c>
       <c r="C211">
         <v>652</v>
@@ -16576,7 +16734,7 @@
         <v>210</v>
       </c>
       <c r="B212" t="s">
-        <v>212</v>
+        <v>234</v>
       </c>
       <c r="C212">
         <v>855</v>
@@ -16647,7 +16805,7 @@
         <v>211</v>
       </c>
       <c r="B213" t="s">
-        <v>213</v>
+        <v>235</v>
       </c>
       <c r="C213">
         <v>856</v>
@@ -16718,7 +16876,7 @@
         <v>212</v>
       </c>
       <c r="B214" t="s">
-        <v>214</v>
+        <v>236</v>
       </c>
       <c r="C214">
         <v>883</v>
@@ -16789,7 +16947,7 @@
         <v>213</v>
       </c>
       <c r="B215" t="s">
-        <v>215</v>
+        <v>237</v>
       </c>
       <c r="C215">
         <v>809</v>
@@ -16860,7 +17018,7 @@
         <v>214</v>
       </c>
       <c r="B216" t="s">
-        <v>216</v>
+        <v>238</v>
       </c>
       <c r="C216">
         <v>913</v>
@@ -16931,7 +17089,7 @@
         <v>215</v>
       </c>
       <c r="B217" t="s">
-        <v>217</v>
+        <v>239</v>
       </c>
       <c r="C217">
         <v>947</v>
@@ -17002,7 +17160,7 @@
         <v>216</v>
       </c>
       <c r="B218" t="s">
-        <v>218</v>
+        <v>240</v>
       </c>
       <c r="C218">
         <v>967</v>
@@ -17073,7 +17231,7 @@
         <v>217</v>
       </c>
       <c r="B219" t="s">
-        <v>219</v>
+        <v>241</v>
       </c>
       <c r="C219">
         <v>711</v>
@@ -17144,7 +17302,7 @@
         <v>218</v>
       </c>
       <c r="B220" t="s">
-        <v>220</v>
+        <v>242</v>
       </c>
       <c r="C220">
         <v>671</v>
@@ -17215,7 +17373,7 @@
         <v>219</v>
       </c>
       <c r="B221" t="s">
-        <v>221</v>
+        <v>243</v>
       </c>
       <c r="C221">
         <v>828</v>
@@ -17286,7 +17444,7 @@
         <v>220</v>
       </c>
       <c r="B222" t="s">
-        <v>222</v>
+        <v>244</v>
       </c>
       <c r="C222">
         <v>563</v>
@@ -17357,7 +17515,7 @@
         <v>221</v>
       </c>
       <c r="B223" t="s">
-        <v>223</v>
+        <v>245</v>
       </c>
       <c r="C223">
         <v>737</v>
@@ -17428,7 +17586,7 @@
         <v>222</v>
       </c>
       <c r="B224" t="s">
-        <v>224</v>
+        <v>246</v>
       </c>
       <c r="C224">
         <v>625</v>
@@ -17499,7 +17657,7 @@
         <v>223</v>
       </c>
       <c r="B225" t="s">
-        <v>225</v>
+        <v>247</v>
       </c>
       <c r="C225">
         <v>706</v>
@@ -17570,7 +17728,7 @@
         <v>224</v>
       </c>
       <c r="B226" t="s">
-        <v>226</v>
+        <v>248</v>
       </c>
       <c r="C226">
         <v>709</v>
@@ -17641,7 +17799,7 @@
         <v>225</v>
       </c>
       <c r="B227" t="s">
-        <v>227</v>
+        <v>249</v>
       </c>
       <c r="C227">
         <v>1012</v>
@@ -17712,7 +17870,7 @@
         <v>226</v>
       </c>
       <c r="B228" t="s">
-        <v>228</v>
+        <v>250</v>
       </c>
       <c r="C228">
         <v>853</v>
@@ -17783,7 +17941,7 @@
         <v>227</v>
       </c>
       <c r="B229" t="s">
-        <v>229</v>
+        <v>251</v>
       </c>
       <c r="C229">
         <v>1198</v>
@@ -17854,7 +18012,7 @@
         <v>228</v>
       </c>
       <c r="B230" t="s">
-        <v>230</v>
+        <v>252</v>
       </c>
       <c r="C230">
         <v>1162</v>
@@ -17925,7 +18083,7 @@
         <v>229</v>
       </c>
       <c r="B231" t="s">
-        <v>231</v>
+        <v>253</v>
       </c>
       <c r="C231">
         <v>1103</v>
@@ -17996,7 +18154,7 @@
         <v>230</v>
       </c>
       <c r="B232" t="s">
-        <v>232</v>
+        <v>254</v>
       </c>
       <c r="C232">
         <v>1066</v>
@@ -18067,7 +18225,7 @@
         <v>231</v>
       </c>
       <c r="B233" t="s">
-        <v>233</v>
+        <v>255</v>
       </c>
       <c r="C233">
         <v>842</v>
@@ -18138,7 +18296,7 @@
         <v>232</v>
       </c>
       <c r="B234" t="s">
-        <v>234</v>
+        <v>256</v>
       </c>
       <c r="C234">
         <v>806</v>
@@ -18209,7 +18367,7 @@
         <v>233</v>
       </c>
       <c r="B235" t="s">
-        <v>235</v>
+        <v>257</v>
       </c>
       <c r="C235">
         <v>668</v>
@@ -18280,7 +18438,7 @@
         <v>234</v>
       </c>
       <c r="B236" t="s">
-        <v>236</v>
+        <v>258</v>
       </c>
       <c r="C236">
         <v>872</v>
@@ -18351,7 +18509,7 @@
         <v>235</v>
       </c>
       <c r="B237" t="s">
-        <v>237</v>
+        <v>259</v>
       </c>
       <c r="C237">
         <v>987</v>
@@ -18422,7 +18580,7 @@
         <v>236</v>
       </c>
       <c r="B238" t="s">
-        <v>238</v>
+        <v>260</v>
       </c>
       <c r="C238">
         <v>864</v>
@@ -18493,7 +18651,7 @@
         <v>237</v>
       </c>
       <c r="B239" t="s">
-        <v>239</v>
+        <v>261</v>
       </c>
       <c r="C239">
         <v>1193</v>
@@ -18564,7 +18722,7 @@
         <v>238</v>
       </c>
       <c r="B240" t="s">
-        <v>240</v>
+        <v>262</v>
       </c>
       <c r="C240">
         <v>1063</v>
@@ -18635,7 +18793,7 @@
         <v>239</v>
       </c>
       <c r="B241" t="s">
-        <v>241</v>
+        <v>263</v>
       </c>
       <c r="C241">
         <v>814</v>
@@ -18706,7 +18864,7 @@
         <v>240</v>
       </c>
       <c r="B242" t="s">
-        <v>242</v>
+        <v>264</v>
       </c>
       <c r="C242">
         <v>1028</v>
@@ -18777,7 +18935,7 @@
         <v>241</v>
       </c>
       <c r="B243" t="s">
-        <v>243</v>
+        <v>265</v>
       </c>
       <c r="C243">
         <v>763</v>
@@ -18848,7 +19006,7 @@
         <v>242</v>
       </c>
       <c r="B244" t="s">
-        <v>244</v>
+        <v>266</v>
       </c>
       <c r="C244">
         <v>774</v>
@@ -18919,7 +19077,7 @@
         <v>243</v>
       </c>
       <c r="B245" t="s">
-        <v>245</v>
+        <v>267</v>
       </c>
       <c r="C245">
         <v>873</v>
@@ -18990,7 +19148,7 @@
         <v>244</v>
       </c>
       <c r="B246" t="s">
-        <v>246</v>
+        <v>268</v>
       </c>
       <c r="C246">
         <v>1060</v>
@@ -19061,7 +19219,7 @@
         <v>245</v>
       </c>
       <c r="B247" t="s">
-        <v>247</v>
+        <v>269</v>
       </c>
       <c r="C247">
         <v>975</v>
@@ -19132,7 +19290,7 @@
         <v>246</v>
       </c>
       <c r="B248" t="s">
-        <v>248</v>
+        <v>270</v>
       </c>
       <c r="C248">
         <v>1152</v>
@@ -19203,7 +19361,7 @@
         <v>247</v>
       </c>
       <c r="B249" t="s">
-        <v>249</v>
+        <v>271</v>
       </c>
       <c r="C249">
         <v>1191</v>
@@ -19274,7 +19432,7 @@
         <v>248</v>
       </c>
       <c r="B250" t="s">
-        <v>250</v>
+        <v>272</v>
       </c>
       <c r="C250">
         <v>813</v>
@@ -19345,7 +19503,7 @@
         <v>249</v>
       </c>
       <c r="B251" t="s">
-        <v>251</v>
+        <v>273</v>
       </c>
       <c r="C251">
         <v>993</v>
@@ -19416,7 +19574,7 @@
         <v>250</v>
       </c>
       <c r="B252" t="s">
-        <v>252</v>
+        <v>274</v>
       </c>
       <c r="C252">
         <v>835</v>
@@ -19487,7 +19645,7 @@
         <v>251</v>
       </c>
       <c r="B253" t="s">
-        <v>253</v>
+        <v>275</v>
       </c>
       <c r="C253">
         <v>982</v>
@@ -19558,7 +19716,7 @@
         <v>252</v>
       </c>
       <c r="B254" t="s">
-        <v>254</v>
+        <v>276</v>
       </c>
       <c r="C254">
         <v>740</v>
@@ -19629,7 +19787,7 @@
         <v>253</v>
       </c>
       <c r="B255" t="s">
-        <v>255</v>
+        <v>277</v>
       </c>
       <c r="C255">
         <v>905</v>
@@ -19700,7 +19858,7 @@
         <v>254</v>
       </c>
       <c r="B256" t="s">
-        <v>256</v>
+        <v>278</v>
       </c>
       <c r="C256">
         <v>829</v>
@@ -19771,7 +19929,7 @@
         <v>255</v>
       </c>
       <c r="B257" t="s">
-        <v>257</v>
+        <v>279</v>
       </c>
       <c r="C257">
         <v>668</v>
@@ -19842,7 +20000,7 @@
         <v>256</v>
       </c>
       <c r="B258" t="s">
-        <v>258</v>
+        <v>280</v>
       </c>
       <c r="C258">
         <v>940</v>
@@ -19913,7 +20071,7 @@
         <v>257</v>
       </c>
       <c r="B259" t="s">
-        <v>259</v>
+        <v>281</v>
       </c>
       <c r="C259">
         <v>924</v>
@@ -19984,7 +20142,7 @@
         <v>258</v>
       </c>
       <c r="B260" t="s">
-        <v>260</v>
+        <v>282</v>
       </c>
       <c r="C260">
         <v>594</v>
@@ -20055,7 +20213,7 @@
         <v>259</v>
       </c>
       <c r="B261" t="s">
-        <v>261</v>
+        <v>283</v>
       </c>
       <c r="C261">
         <v>1025</v>
@@ -20126,7 +20284,7 @@
         <v>260</v>
       </c>
       <c r="B262" t="s">
-        <v>262</v>
+        <v>284</v>
       </c>
       <c r="C262">
         <v>1033</v>
@@ -20197,7 +20355,7 @@
         <v>261</v>
       </c>
       <c r="B263" t="s">
-        <v>263</v>
+        <v>285</v>
       </c>
       <c r="C263">
         <v>883</v>
@@ -20268,7 +20426,7 @@
         <v>262</v>
       </c>
       <c r="B264" t="s">
-        <v>264</v>
+        <v>286</v>
       </c>
       <c r="C264">
         <v>1020</v>
@@ -20339,7 +20497,7 @@
         <v>263</v>
       </c>
       <c r="B265" t="s">
-        <v>265</v>
+        <v>287</v>
       </c>
       <c r="C265">
         <v>732</v>
@@ -20410,7 +20568,7 @@
         <v>264</v>
       </c>
       <c r="B266" t="s">
-        <v>266</v>
+        <v>288</v>
       </c>
       <c r="C266">
         <v>811</v>
@@ -20481,7 +20639,7 @@
         <v>265</v>
       </c>
       <c r="B267" t="s">
-        <v>267</v>
+        <v>289</v>
       </c>
       <c r="C267">
         <v>736</v>
@@ -20552,7 +20710,7 @@
         <v>266</v>
       </c>
       <c r="B268" t="s">
-        <v>268</v>
+        <v>290</v>
       </c>
       <c r="C268">
         <v>732</v>
@@ -20623,7 +20781,7 @@
         <v>267</v>
       </c>
       <c r="B269" t="s">
-        <v>269</v>
+        <v>291</v>
       </c>
       <c r="C269">
         <v>760</v>
@@ -20694,7 +20852,7 @@
         <v>268</v>
       </c>
       <c r="B270" t="s">
-        <v>270</v>
+        <v>292</v>
       </c>
       <c r="C270">
         <v>762</v>
@@ -20765,7 +20923,7 @@
         <v>269</v>
       </c>
       <c r="B271" t="s">
-        <v>271</v>
+        <v>293</v>
       </c>
       <c r="C271">
         <v>771</v>
@@ -20836,7 +20994,7 @@
         <v>270</v>
       </c>
       <c r="B272" t="s">
-        <v>272</v>
+        <v>294</v>
       </c>
       <c r="C272">
         <v>870</v>
@@ -20907,7 +21065,7 @@
         <v>271</v>
       </c>
       <c r="B273" t="s">
-        <v>273</v>
+        <v>295</v>
       </c>
       <c r="C273">
         <v>725</v>
@@ -20978,7 +21136,7 @@
         <v>272</v>
       </c>
       <c r="B274" t="s">
-        <v>274</v>
+        <v>296</v>
       </c>
       <c r="C274">
         <v>538</v>
@@ -21049,7 +21207,7 @@
         <v>273</v>
       </c>
       <c r="B275" t="s">
-        <v>275</v>
+        <v>297</v>
       </c>
       <c r="C275">
         <v>701</v>
@@ -21120,7 +21278,7 @@
         <v>274</v>
       </c>
       <c r="B276" t="s">
-        <v>276</v>
+        <v>298</v>
       </c>
       <c r="C276">
         <v>973</v>
@@ -21191,7 +21349,7 @@
         <v>275</v>
       </c>
       <c r="B277" t="s">
-        <v>277</v>
+        <v>299</v>
       </c>
       <c r="C277">
         <v>684</v>
@@ -21262,7 +21420,7 @@
         <v>276</v>
       </c>
       <c r="B278" t="s">
-        <v>278</v>
+        <v>300</v>
       </c>
       <c r="C278">
         <v>679</v>
@@ -21333,7 +21491,7 @@
         <v>277</v>
       </c>
       <c r="B279" t="s">
-        <v>279</v>
+        <v>301</v>
       </c>
       <c r="C279">
         <v>988</v>
@@ -21404,7 +21562,7 @@
         <v>278</v>
       </c>
       <c r="B280" t="s">
-        <v>280</v>
+        <v>302</v>
       </c>
       <c r="C280">
         <v>776</v>
@@ -21475,7 +21633,7 @@
         <v>279</v>
       </c>
       <c r="B281" t="s">
-        <v>281</v>
+        <v>303</v>
       </c>
       <c r="C281">
         <v>1141</v>
@@ -21546,7 +21704,7 @@
         <v>280</v>
       </c>
       <c r="B282" t="s">
-        <v>282</v>
+        <v>304</v>
       </c>
       <c r="C282">
         <v>1113</v>
@@ -21617,7 +21775,7 @@
         <v>281</v>
       </c>
       <c r="B283" t="s">
-        <v>283</v>
+        <v>305</v>
       </c>
       <c r="C283">
         <v>667</v>
@@ -21688,7 +21846,7 @@
         <v>282</v>
       </c>
       <c r="B284" t="s">
-        <v>284</v>
+        <v>306</v>
       </c>
       <c r="C284">
         <v>650</v>
@@ -21759,7 +21917,7 @@
         <v>283</v>
       </c>
       <c r="B285" t="s">
-        <v>285</v>
+        <v>307</v>
       </c>
       <c r="C285">
         <v>969</v>
@@ -21830,7 +21988,7 @@
         <v>284</v>
       </c>
       <c r="B286" t="s">
-        <v>286</v>
+        <v>308</v>
       </c>
       <c r="C286">
         <v>1029</v>
@@ -21901,7 +22059,7 @@
         <v>285</v>
       </c>
       <c r="B287" t="s">
-        <v>287</v>
+        <v>309</v>
       </c>
       <c r="C287">
         <v>799</v>
@@ -21972,7 +22130,7 @@
         <v>286</v>
       </c>
       <c r="B288" t="s">
-        <v>288</v>
+        <v>310</v>
       </c>
       <c r="C288">
         <v>564</v>
@@ -22043,7 +22201,7 @@
         <v>287</v>
       </c>
       <c r="B289" t="s">
-        <v>289</v>
+        <v>311</v>
       </c>
       <c r="C289">
         <v>903</v>
@@ -22114,7 +22272,7 @@
         <v>288</v>
       </c>
       <c r="B290" t="s">
-        <v>290</v>
+        <v>312</v>
       </c>
       <c r="C290">
         <v>938</v>
@@ -22185,7 +22343,7 @@
         <v>289</v>
       </c>
       <c r="B291" t="s">
-        <v>291</v>
+        <v>313</v>
       </c>
       <c r="C291">
         <v>573</v>
@@ -22256,7 +22414,7 @@
         <v>290</v>
       </c>
       <c r="B292" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="C292">
         <v>790</v>
@@ -22327,7 +22485,7 @@
         <v>291</v>
       </c>
       <c r="B293" t="s">
-        <v>293</v>
+        <v>315</v>
       </c>
       <c r="C293">
         <v>636</v>
@@ -22398,7 +22556,7 @@
         <v>292</v>
       </c>
       <c r="B294" t="s">
-        <v>294</v>
+        <v>316</v>
       </c>
       <c r="C294">
         <v>599</v>
@@ -22469,7 +22627,7 @@
         <v>293</v>
       </c>
       <c r="B295" t="s">
-        <v>295</v>
+        <v>317</v>
       </c>
       <c r="C295">
         <v>540</v>
@@ -22540,7 +22698,7 @@
         <v>294</v>
       </c>
       <c r="B296" t="s">
-        <v>296</v>
+        <v>318</v>
       </c>
       <c r="C296">
         <v>789</v>
@@ -22611,7 +22769,7 @@
         <v>295</v>
       </c>
       <c r="B297" t="s">
-        <v>297</v>
+        <v>319</v>
       </c>
       <c r="C297">
         <v>730</v>
@@ -22682,7 +22840,7 @@
         <v>296</v>
       </c>
       <c r="B298" t="s">
-        <v>298</v>
+        <v>320</v>
       </c>
       <c r="C298">
         <v>830</v>
@@ -22753,7 +22911,7 @@
         <v>297</v>
       </c>
       <c r="B299" t="s">
-        <v>299</v>
+        <v>321</v>
       </c>
       <c r="C299">
         <v>616</v>
@@ -22824,7 +22982,7 @@
         <v>298</v>
       </c>
       <c r="B300" t="s">
-        <v>300</v>
+        <v>322</v>
       </c>
       <c r="C300">
         <v>633</v>
@@ -22895,7 +23053,7 @@
         <v>299</v>
       </c>
       <c r="B301" t="s">
-        <v>301</v>
+        <v>323</v>
       </c>
       <c r="C301">
         <v>651</v>
@@ -22966,7 +23124,7 @@
         <v>300</v>
       </c>
       <c r="B302" t="s">
-        <v>302</v>
+        <v>324</v>
       </c>
       <c r="C302">
         <v>817</v>
@@ -23037,7 +23195,7 @@
         <v>301</v>
       </c>
       <c r="B303" t="s">
-        <v>303</v>
+        <v>325</v>
       </c>
       <c r="C303">
         <v>748</v>
@@ -23108,7 +23266,7 @@
         <v>302</v>
       </c>
       <c r="B304" t="s">
-        <v>304</v>
+        <v>326</v>
       </c>
       <c r="C304">
         <v>838</v>
@@ -23179,7 +23337,7 @@
         <v>303</v>
       </c>
       <c r="B305" t="s">
-        <v>305</v>
+        <v>327</v>
       </c>
       <c r="C305">
         <v>804</v>
@@ -23250,7 +23408,7 @@
         <v>304</v>
       </c>
       <c r="B306" t="s">
-        <v>306</v>
+        <v>328</v>
       </c>
       <c r="C306">
         <v>722</v>
@@ -23321,7 +23479,7 @@
         <v>305</v>
       </c>
       <c r="B307" t="s">
-        <v>307</v>
+        <v>329</v>
       </c>
       <c r="C307">
         <v>756</v>
@@ -23392,7 +23550,7 @@
         <v>306</v>
       </c>
       <c r="B308" t="s">
-        <v>308</v>
+        <v>330</v>
       </c>
       <c r="C308">
         <v>799</v>
@@ -23463,7 +23621,7 @@
         <v>307</v>
       </c>
       <c r="B309" t="s">
-        <v>309</v>
+        <v>331</v>
       </c>
       <c r="C309">
         <v>592</v>
@@ -23534,7 +23692,7 @@
         <v>308</v>
       </c>
       <c r="B310" t="s">
-        <v>310</v>
+        <v>332</v>
       </c>
       <c r="C310">
         <v>961</v>
@@ -23605,7 +23763,7 @@
         <v>309</v>
       </c>
       <c r="B311" t="s">
-        <v>311</v>
+        <v>333</v>
       </c>
       <c r="C311">
         <v>568</v>
@@ -23676,7 +23834,7 @@
         <v>310</v>
       </c>
       <c r="B312" t="s">
-        <v>312</v>
+        <v>334</v>
       </c>
       <c r="C312">
         <v>622</v>
@@ -23747,7 +23905,7 @@
         <v>311</v>
       </c>
       <c r="B313" t="s">
-        <v>313</v>
+        <v>335</v>
       </c>
       <c r="C313">
         <v>643</v>
@@ -23818,7 +23976,7 @@
         <v>312</v>
       </c>
       <c r="B314" t="s">
-        <v>314</v>
+        <v>336</v>
       </c>
       <c r="C314">
         <v>664</v>
@@ -23889,7 +24047,7 @@
         <v>313</v>
       </c>
       <c r="B315" t="s">
-        <v>315</v>
+        <v>337</v>
       </c>
       <c r="C315">
         <v>641</v>
@@ -23960,7 +24118,7 @@
         <v>314</v>
       </c>
       <c r="B316" t="s">
-        <v>316</v>
+        <v>338</v>
       </c>
       <c r="C316">
         <v>683</v>
@@ -24031,7 +24189,7 @@
         <v>315</v>
       </c>
       <c r="B317" t="s">
-        <v>317</v>
+        <v>339</v>
       </c>
       <c r="C317">
         <v>629</v>
@@ -24102,7 +24260,7 @@
         <v>316</v>
       </c>
       <c r="B318" t="s">
-        <v>318</v>
+        <v>340</v>
       </c>
       <c r="C318">
         <v>1109</v>
@@ -24173,7 +24331,7 @@
         <v>317</v>
       </c>
       <c r="B319" t="s">
-        <v>319</v>
+        <v>341</v>
       </c>
       <c r="C319">
         <v>1007</v>
@@ -24244,7 +24402,7 @@
         <v>318</v>
       </c>
       <c r="B320" t="s">
-        <v>320</v>
+        <v>342</v>
       </c>
       <c r="C320">
         <v>597</v>
@@ -24315,7 +24473,7 @@
         <v>319</v>
       </c>
       <c r="B321" t="s">
-        <v>321</v>
+        <v>343</v>
       </c>
       <c r="C321">
         <v>838</v>
@@ -24386,7 +24544,7 @@
         <v>320</v>
       </c>
       <c r="B322" t="s">
-        <v>322</v>
+        <v>344</v>
       </c>
       <c r="C322">
         <v>821</v>
@@ -24457,7 +24615,7 @@
         <v>321</v>
       </c>
       <c r="B323" t="s">
-        <v>323</v>
+        <v>345</v>
       </c>
       <c r="C323">
         <v>421</v>
@@ -24528,7 +24686,7 @@
         <v>322</v>
       </c>
       <c r="B324" t="s">
-        <v>324</v>
+        <v>346</v>
       </c>
       <c r="C324">
         <v>1030</v>
@@ -24599,7 +24757,7 @@
         <v>323</v>
       </c>
       <c r="B325" t="s">
-        <v>325</v>
+        <v>347</v>
       </c>
       <c r="C325">
         <v>994</v>
@@ -24670,7 +24828,7 @@
         <v>324</v>
       </c>
       <c r="B326" t="s">
-        <v>326</v>
+        <v>348</v>
       </c>
       <c r="C326">
         <v>493</v>
@@ -24741,7 +24899,7 @@
         <v>325</v>
       </c>
       <c r="B327" t="s">
-        <v>327</v>
+        <v>349</v>
       </c>
       <c r="C327">
         <v>619</v>
@@ -24812,7 +24970,7 @@
         <v>326</v>
       </c>
       <c r="B328" t="s">
-        <v>328</v>
+        <v>350</v>
       </c>
       <c r="C328">
         <v>591</v>
@@ -24883,7 +25041,7 @@
         <v>327</v>
       </c>
       <c r="B329" t="s">
-        <v>329</v>
+        <v>351</v>
       </c>
       <c r="C329">
         <v>1144</v>
@@ -24954,7 +25112,7 @@
         <v>328</v>
       </c>
       <c r="B330" t="s">
-        <v>330</v>
+        <v>352</v>
       </c>
       <c r="C330">
         <v>1118</v>
@@ -25025,7 +25183,7 @@
         <v>329</v>
       </c>
       <c r="B331" t="s">
-        <v>331</v>
+        <v>353</v>
       </c>
       <c r="C331">
         <v>583</v>
@@ -25096,7 +25254,7 @@
         <v>330</v>
       </c>
       <c r="B332" t="s">
-        <v>332</v>
+        <v>354</v>
       </c>
       <c r="C332">
         <v>600</v>
@@ -25167,7 +25325,7 @@
         <v>331</v>
       </c>
       <c r="B333" t="s">
-        <v>333</v>
+        <v>355</v>
       </c>
       <c r="C333">
         <v>528</v>
@@ -25238,7 +25396,7 @@
         <v>332</v>
       </c>
       <c r="B334" t="s">
-        <v>334</v>
+        <v>356</v>
       </c>
       <c r="C334">
         <v>707</v>
@@ -25309,7 +25467,7 @@
         <v>333</v>
       </c>
       <c r="B335" t="s">
-        <v>335</v>
+        <v>357</v>
       </c>
       <c r="C335">
         <v>737</v>
@@ -25380,7 +25538,7 @@
         <v>334</v>
       </c>
       <c r="B336" t="s">
-        <v>336</v>
+        <v>358</v>
       </c>
       <c r="C336">
         <v>788</v>
@@ -25451,7 +25609,7 @@
         <v>335</v>
       </c>
       <c r="B337" t="s">
-        <v>337</v>
+        <v>359</v>
       </c>
       <c r="C337">
         <v>751</v>
@@ -25522,7 +25680,7 @@
         <v>336</v>
       </c>
       <c r="B338" t="s">
-        <v>338</v>
+        <v>360</v>
       </c>
       <c r="C338">
         <v>842</v>
@@ -25593,7 +25751,7 @@
         <v>337</v>
       </c>
       <c r="B339" t="s">
-        <v>339</v>
+        <v>361</v>
       </c>
       <c r="C339">
         <v>867</v>
@@ -25664,7 +25822,7 @@
         <v>338</v>
       </c>
       <c r="B340" t="s">
-        <v>340</v>
+        <v>362</v>
       </c>
       <c r="C340">
         <v>1116</v>
@@ -25735,7 +25893,7 @@
         <v>339</v>
       </c>
       <c r="B341" t="s">
-        <v>341</v>
+        <v>363</v>
       </c>
       <c r="C341">
         <v>1019</v>
@@ -25806,7 +25964,7 @@
         <v>340</v>
       </c>
       <c r="B342" t="s">
-        <v>342</v>
+        <v>364</v>
       </c>
       <c r="C342">
         <v>913</v>
@@ -25877,7 +26035,7 @@
         <v>341</v>
       </c>
       <c r="B343" t="s">
-        <v>343</v>
+        <v>365</v>
       </c>
       <c r="C343">
         <v>698</v>
@@ -25948,7 +26106,7 @@
         <v>342</v>
       </c>
       <c r="B344" t="s">
-        <v>344</v>
+        <v>366</v>
       </c>
       <c r="C344">
         <v>686</v>
@@ -26019,7 +26177,7 @@
         <v>343</v>
       </c>
       <c r="B345" t="s">
-        <v>345</v>
+        <v>367</v>
       </c>
       <c r="C345">
         <v>513</v>
@@ -26090,7 +26248,7 @@
         <v>344</v>
       </c>
       <c r="B346" t="s">
-        <v>346</v>
+        <v>368</v>
       </c>
       <c r="C346">
         <v>422</v>
@@ -26161,7 +26319,7 @@
         <v>345</v>
       </c>
       <c r="B347" t="s">
-        <v>347</v>
+        <v>369</v>
       </c>
       <c r="C347">
         <v>593</v>
@@ -26232,7 +26390,7 @@
         <v>346</v>
       </c>
       <c r="B348" t="s">
-        <v>348</v>
+        <v>370</v>
       </c>
       <c r="C348">
         <v>1166</v>
@@ -26303,7 +26461,7 @@
         <v>347</v>
       </c>
       <c r="B349" t="s">
-        <v>349</v>
+        <v>371</v>
       </c>
       <c r="C349">
         <v>978</v>
@@ -26374,7 +26532,7 @@
         <v>348</v>
       </c>
       <c r="B350" t="s">
-        <v>350</v>
+        <v>372</v>
       </c>
       <c r="C350">
         <v>903</v>
@@ -26445,7 +26603,7 @@
         <v>349</v>
       </c>
       <c r="B351" t="s">
-        <v>351</v>
+        <v>373</v>
       </c>
       <c r="C351">
         <v>799</v>
@@ -26516,7 +26674,7 @@
         <v>350</v>
       </c>
       <c r="B352" t="s">
-        <v>352</v>
+        <v>374</v>
       </c>
       <c r="C352">
         <v>918</v>
@@ -26587,7 +26745,7 @@
         <v>351</v>
       </c>
       <c r="B353" t="s">
-        <v>353</v>
+        <v>375</v>
       </c>
       <c r="C353">
         <v>882</v>
@@ -26658,7 +26816,7 @@
         <v>352</v>
       </c>
       <c r="B354" t="s">
-        <v>354</v>
+        <v>376</v>
       </c>
       <c r="C354">
         <v>898</v>
@@ -26729,7 +26887,7 @@
         <v>353</v>
       </c>
       <c r="B355" t="s">
-        <v>355</v>
+        <v>377</v>
       </c>
       <c r="C355">
         <v>951</v>
@@ -26800,7 +26958,7 @@
         <v>354</v>
       </c>
       <c r="B356" t="s">
-        <v>356</v>
+        <v>378</v>
       </c>
       <c r="C356">
         <v>952</v>
@@ -26871,7 +27029,7 @@
         <v>355</v>
       </c>
       <c r="B357" t="s">
-        <v>357</v>
+        <v>379</v>
       </c>
       <c r="C357">
         <v>925</v>
@@ -26942,7 +27100,7 @@
         <v>356</v>
       </c>
       <c r="B358" t="s">
-        <v>358</v>
+        <v>380</v>
       </c>
       <c r="C358">
         <v>1057</v>
@@ -27013,7 +27171,7 @@
         <v>357</v>
       </c>
       <c r="B359" t="s">
-        <v>359</v>
+        <v>381</v>
       </c>
       <c r="C359">
         <v>901</v>
@@ -27084,7 +27242,7 @@
         <v>358</v>
       </c>
       <c r="B360" t="s">
-        <v>360</v>
+        <v>382</v>
       </c>
       <c r="C360">
         <v>763</v>
@@ -27155,7 +27313,7 @@
         <v>359</v>
       </c>
       <c r="B361" t="s">
-        <v>361</v>
+        <v>383</v>
       </c>
       <c r="C361">
         <v>790</v>
@@ -27226,7 +27384,7 @@
         <v>360</v>
       </c>
       <c r="B362" t="s">
-        <v>362</v>
+        <v>384</v>
       </c>
       <c r="C362">
         <v>711</v>
@@ -27297,7 +27455,7 @@
         <v>361</v>
       </c>
       <c r="B363" t="s">
-        <v>363</v>
+        <v>385</v>
       </c>
       <c r="C363">
         <v>702</v>
@@ -27368,7 +27526,7 @@
         <v>362</v>
       </c>
       <c r="B364" t="s">
-        <v>364</v>
+        <v>386</v>
       </c>
       <c r="C364">
         <v>954</v>
@@ -27439,7 +27597,7 @@
         <v>363</v>
       </c>
       <c r="B365" t="s">
-        <v>365</v>
+        <v>387</v>
       </c>
       <c r="C365">
         <v>472</v>
@@ -27510,7 +27668,7 @@
         <v>364</v>
       </c>
       <c r="B366" t="s">
-        <v>366</v>
+        <v>388</v>
       </c>
       <c r="C366">
         <v>770</v>
@@ -27581,7 +27739,7 @@
         <v>365</v>
       </c>
       <c r="B367" t="s">
-        <v>367</v>
+        <v>389</v>
       </c>
       <c r="C367">
         <v>732</v>
@@ -27652,7 +27810,7 @@
         <v>366</v>
       </c>
       <c r="B368" t="s">
-        <v>368</v>
+        <v>390</v>
       </c>
       <c r="C368">
         <v>825</v>
@@ -27723,7 +27881,7 @@
         <v>367</v>
       </c>
       <c r="B369" t="s">
-        <v>369</v>
+        <v>391</v>
       </c>
       <c r="C369">
         <v>902</v>
@@ -27794,7 +27952,7 @@
         <v>368</v>
       </c>
       <c r="B370" t="s">
-        <v>370</v>
+        <v>392</v>
       </c>
       <c r="C370">
         <v>681</v>
@@ -27865,7 +28023,7 @@
         <v>369</v>
       </c>
       <c r="B371" t="s">
-        <v>371</v>
+        <v>393</v>
       </c>
       <c r="C371">
         <v>680</v>
@@ -27936,7 +28094,7 @@
         <v>370</v>
       </c>
       <c r="B372" t="s">
-        <v>372</v>
+        <v>394</v>
       </c>
       <c r="C372">
         <v>1055</v>
@@ -28007,7 +28165,7 @@
         <v>371</v>
       </c>
       <c r="B373" t="s">
-        <v>373</v>
+        <v>395</v>
       </c>
       <c r="C373">
         <v>644</v>
@@ -28078,7 +28236,7 @@
         <v>372</v>
       </c>
       <c r="B374" t="s">
-        <v>374</v>
+        <v>396</v>
       </c>
       <c r="C374">
         <v>886</v>
@@ -28149,7 +28307,7 @@
         <v>373</v>
       </c>
       <c r="B375" t="s">
-        <v>375</v>
+        <v>397</v>
       </c>
       <c r="C375">
         <v>543</v>
@@ -28220,7 +28378,7 @@
         <v>374</v>
       </c>
       <c r="B376" t="s">
-        <v>376</v>
+        <v>398</v>
       </c>
       <c r="C376">
         <v>883</v>
@@ -28291,7 +28449,7 @@
         <v>375</v>
       </c>
       <c r="B377" t="s">
-        <v>377</v>
+        <v>399</v>
       </c>
       <c r="C377">
         <v>557</v>
@@ -28362,7 +28520,7 @@
         <v>376</v>
       </c>
       <c r="B378" t="s">
-        <v>378</v>
+        <v>400</v>
       </c>
       <c r="C378">
         <v>752</v>
@@ -28433,7 +28591,7 @@
         <v>377</v>
       </c>
       <c r="B379" t="s">
-        <v>379</v>
+        <v>401</v>
       </c>
       <c r="C379">
         <v>774</v>
@@ -28504,7 +28662,7 @@
         <v>378</v>
       </c>
       <c r="B380" t="s">
-        <v>380</v>
+        <v>402</v>
       </c>
       <c r="C380">
         <v>831</v>
@@ -28575,7 +28733,7 @@
         <v>379</v>
       </c>
       <c r="B381" t="s">
-        <v>381</v>
+        <v>403</v>
       </c>
       <c r="C381">
         <v>738</v>
@@ -28646,7 +28804,7 @@
         <v>380</v>
       </c>
       <c r="B382" t="s">
-        <v>382</v>
+        <v>404</v>
       </c>
       <c r="C382">
         <v>692</v>
@@ -28717,7 +28875,7 @@
         <v>381</v>
       </c>
       <c r="B383" t="s">
-        <v>383</v>
+        <v>405</v>
       </c>
       <c r="C383">
         <v>681</v>
@@ -28788,7 +28946,7 @@
         <v>382</v>
       </c>
       <c r="B384" t="s">
-        <v>384</v>
+        <v>406</v>
       </c>
       <c r="C384">
         <v>705</v>
@@ -28859,7 +29017,7 @@
         <v>383</v>
       </c>
       <c r="B385" t="s">
-        <v>385</v>
+        <v>407</v>
       </c>
       <c r="C385">
         <v>741</v>
@@ -28930,7 +29088,7 @@
         <v>384</v>
       </c>
       <c r="B386" t="s">
-        <v>386</v>
+        <v>408</v>
       </c>
       <c r="C386">
         <v>1110</v>
@@ -29001,7 +29159,7 @@
         <v>385</v>
       </c>
       <c r="B387" t="s">
-        <v>387</v>
+        <v>409</v>
       </c>
       <c r="C387">
         <v>633</v>
@@ -29072,7 +29230,7 @@
         <v>386</v>
       </c>
       <c r="B388" t="s">
-        <v>388</v>
+        <v>410</v>
       </c>
       <c r="C388">
         <v>626</v>
@@ -29143,7 +29301,7 @@
         <v>387</v>
       </c>
       <c r="B389" t="s">
-        <v>389</v>
+        <v>411</v>
       </c>
       <c r="C389">
         <v>786</v>
@@ -29214,7 +29372,7 @@
         <v>388</v>
       </c>
       <c r="B390" t="s">
-        <v>390</v>
+        <v>412</v>
       </c>
       <c r="C390">
         <v>796</v>
@@ -29285,7 +29443,7 @@
         <v>389</v>
       </c>
       <c r="B391" t="s">
-        <v>391</v>
+        <v>413</v>
       </c>
       <c r="C391">
         <v>859</v>
@@ -29356,7 +29514,7 @@
         <v>390</v>
       </c>
       <c r="B392" t="s">
-        <v>392</v>
+        <v>414</v>
       </c>
       <c r="C392">
         <v>829</v>
@@ -29427,7 +29585,7 @@
         <v>391</v>
       </c>
       <c r="B393" t="s">
-        <v>393</v>
+        <v>415</v>
       </c>
       <c r="C393">
         <v>565</v>
@@ -29498,7 +29656,7 @@
         <v>392</v>
       </c>
       <c r="B394" t="s">
-        <v>394</v>
+        <v>416</v>
       </c>
       <c r="C394">
         <v>643</v>
@@ -29569,7 +29727,7 @@
         <v>393</v>
       </c>
       <c r="B395" t="s">
-        <v>395</v>
+        <v>417</v>
       </c>
       <c r="C395">
         <v>689</v>
@@ -29640,7 +29798,7 @@
         <v>394</v>
       </c>
       <c r="B396" t="s">
-        <v>396</v>
+        <v>418</v>
       </c>
       <c r="C396">
         <v>1141</v>
@@ -29711,7 +29869,7 @@
         <v>395</v>
       </c>
       <c r="B397" t="s">
-        <v>397</v>
+        <v>419</v>
       </c>
       <c r="C397">
         <v>865</v>
@@ -29782,7 +29940,7 @@
         <v>396</v>
       </c>
       <c r="B398" t="s">
-        <v>398</v>
+        <v>420</v>
       </c>
       <c r="C398">
         <v>1037</v>
@@ -29853,7 +30011,7 @@
         <v>397</v>
       </c>
       <c r="B399" t="s">
-        <v>399</v>
+        <v>421</v>
       </c>
       <c r="C399">
         <v>708</v>
@@ -29924,7 +30082,7 @@
         <v>398</v>
       </c>
       <c r="B400" t="s">
-        <v>400</v>
+        <v>422</v>
       </c>
       <c r="C400">
         <v>664</v>
@@ -29995,7 +30153,7 @@
         <v>399</v>
       </c>
       <c r="B401" t="s">
-        <v>401</v>
+        <v>423</v>
       </c>
       <c r="C401">
         <v>657</v>
@@ -30066,7 +30224,7 @@
         <v>400</v>
       </c>
       <c r="B402" t="s">
-        <v>402</v>
+        <v>424</v>
       </c>
       <c r="C402">
         <v>658</v>
@@ -30137,7 +30295,7 @@
         <v>401</v>
       </c>
       <c r="B403" t="s">
-        <v>403</v>
+        <v>425</v>
       </c>
       <c r="C403">
         <v>749</v>
@@ -30208,7 +30366,7 @@
         <v>402</v>
       </c>
       <c r="B404" t="s">
-        <v>404</v>
+        <v>426</v>
       </c>
       <c r="C404">
         <v>1086</v>
@@ -30279,7 +30437,7 @@
         <v>403</v>
       </c>
       <c r="B405" t="s">
-        <v>405</v>
+        <v>427</v>
       </c>
       <c r="C405">
         <v>633</v>
@@ -30350,7 +30508,7 @@
         <v>404</v>
       </c>
       <c r="B406" t="s">
-        <v>406</v>
+        <v>428</v>
       </c>
       <c r="C406">
         <v>646</v>
@@ -30421,7 +30579,7 @@
         <v>405</v>
       </c>
       <c r="B407" t="s">
-        <v>407</v>
+        <v>429</v>
       </c>
       <c r="C407">
         <v>803</v>
@@ -30492,7 +30650,7 @@
         <v>406</v>
       </c>
       <c r="B408" t="s">
-        <v>408</v>
+        <v>430</v>
       </c>
       <c r="C408">
         <v>844</v>
@@ -30563,7 +30721,7 @@
         <v>407</v>
       </c>
       <c r="B409" t="s">
-        <v>409</v>
+        <v>431</v>
       </c>
       <c r="C409">
         <v>1023</v>
@@ -30634,7 +30792,7 @@
         <v>408</v>
       </c>
       <c r="B410" t="s">
-        <v>410</v>
+        <v>432</v>
       </c>
       <c r="C410">
         <v>585</v>
@@ -30705,7 +30863,7 @@
         <v>409</v>
       </c>
       <c r="B411" t="s">
-        <v>411</v>
+        <v>433</v>
       </c>
       <c r="C411">
         <v>1087</v>
@@ -30776,7 +30934,7 @@
         <v>410</v>
       </c>
       <c r="B412" t="s">
-        <v>412</v>
+        <v>434</v>
       </c>
       <c r="C412">
         <v>865</v>
@@ -30847,7 +31005,7 @@
         <v>411</v>
       </c>
       <c r="B413" t="s">
-        <v>413</v>
+        <v>435</v>
       </c>
       <c r="C413">
         <v>988</v>
@@ -30918,7 +31076,7 @@
         <v>412</v>
       </c>
       <c r="B414" t="s">
-        <v>414</v>
+        <v>436</v>
       </c>
       <c r="C414">
         <v>1095</v>
